--- a/reports/obex/2026-01/obex_settlement_january_2026.xlsx
+++ b/reports/obex/2026-01/obex_settlement_january_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T10:57:50+00:00</t>
+          <t>2026-06-09T16:55:05+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/obex/2026-01/obex_settlement_january_2026.xlsx
+++ b/reports/obex/2026-01/obex_settlement_january_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T16:55:05+00:00</t>
+          <t>2026-06-09T22:25:16+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/obex/2026-01/obex_settlement_january_2026.xlsx
+++ b/reports/obex/2026-01/obex_settlement_january_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T22:25:16+00:00</t>
+          <t>2026-06-09T23:12:22+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/obex/2026-01/obex_settlement_january_2026.xlsx
+++ b/reports/obex/2026-01/obex_settlement_january_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T23:12:22+00:00</t>
+          <t>2026-06-10T10:52:03+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/obex/2026-01/obex_settlement_january_2026.xlsx
+++ b/reports/obex/2026-01/obex_settlement_january_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-10T10:52:03+00:00</t>
+          <t>2026-07-03T07:02:59+00:00</t>
         </is>
       </c>
     </row>
